--- a/userAnalitices/telemetry/United Kingdom_V1.3.2_User03_-e18-_df66.xlsx
+++ b/userAnalitices/telemetry/United Kingdom_V1.3.2_User03_-e18-_df66.xlsx
@@ -761,10 +761,10 @@
         <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
@@ -2335,7 +2335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2933,6 +2933,34 @@
         <v>0</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>⬜ Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>0 min</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>⬜ Inactive</t>
         </is>
